--- a/extra/report/No.追加実習_ソートテスト結果.xlsx
+++ b/extra/report/No.追加実習_ソートテスト結果.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAE7266-DDFF-47A5-A68C-1943B93981CB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5648EA-681B-45A2-AA51-4A28C27AD29A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17415" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17415" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="前提" sheetId="2" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="ケース38－49" sheetId="5" r:id="rId5"/>
     <sheet name="ケース50-61" sheetId="6" r:id="rId6"/>
     <sheet name="ケース62-69" sheetId="7" r:id="rId7"/>
-    <sheet name="ケー70-77" sheetId="8" r:id="rId8"/>
+    <sheet name="ケース70-77" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
